--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crisramirez\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E19A7E-D573-4849-9E8A-D38446A56F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AE2698-FD0E-4FA6-B19D-A456B23DD031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{A2422C35-CD33-4D74-8BEB-AA9B830BA587}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{A2422C35-CD33-4D74-8BEB-AA9B830BA587}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Store</t>
   </si>
@@ -102,31 +102,16 @@
     <t>The average monthly sales across all 12 stores is approximately 49.42.</t>
   </si>
   <si>
-    <t>Overall Average</t>
-  </si>
-  <si>
     <t>The median of 47.5 is lower than the mean, suggesting that a high value is pulling the average up.</t>
   </si>
   <si>
-    <t>Median Comparison</t>
-  </si>
-  <si>
     <t>More stores perform between 43 and 52, showing relatively consistent performance when excluding the outliers.</t>
   </si>
   <si>
-    <t>Consistency</t>
-  </si>
-  <si>
     <t>Store H at 72 significantl influences the mean, range and standard deviation. Removing it would drop from 7.58 to 2.91.</t>
   </si>
   <si>
-    <t>Impact</t>
-  </si>
-  <si>
     <t xml:space="preserve">In conclusion, the spike in store H is very unusual and I would like to know what caused it. </t>
-  </si>
-  <si>
-    <t>Additional Info</t>
   </si>
 </sst>
 </file>
@@ -673,52 +658,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A2B063-7477-41D5-9B23-B98A283FEF59}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
